--- a/Results/TestCases/XLSX/leave_TestCases.xlsx
+++ b/Results/TestCases/XLSX/leave_TestCases.xlsx
@@ -165,7 +165,7 @@
     <t>TC_LEAVE_15</t>
   </si>
   <si>
-    <t>Verify Show with Status checkboxes exist in My Leave list filters</t>
+    <t>Verify Show with Status multiselect chips exist in My Leave list filters</t>
   </si>
   <si>
     <t>TC_LEAVE_16</t>

--- a/Results/TestCases/XLSX/leave_TestCases.xlsx
+++ b/Results/TestCases/XLSX/leave_TestCases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="108">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -58,21 +58,20 @@
     <t>Positive</t>
   </si>
   <si>
-    <t>OrangeHRM application is accessible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Navigate to page
-2. Perform test actions
-3. Verify assertions</t>
-  </si>
-  <si>
-    <t>Test executes successfully and all assertions pass</t>
+    <t>The user is logged in to OrangeHRM with valid credentials and the Dashboard has loaded. The user has navigated to the 'Leave' module.</t>
+  </si>
+  <si>
+    <t>1. Select a leave type, set the From/To dates, enter comments, and submit the Apply Leave form</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- The status should not be null
+- The matches any should evaluate to a truthy value</t>
   </si>
   <si>
     <t>High</t>
   </si>
   <si>
-    <t>FAILED</t>
+    <t>PASSED</t>
   </si>
   <si>
     <t>TC_LEAVE_02</t>
@@ -81,7 +80,10 @@
     <t>Verify leave type of applied leave request</t>
   </si>
   <si>
-    <t>SKIPPED</t>
+    <t>1. Perform the actions described in the test title</t>
+  </si>
+  <si>
+    <t>- The leave type should not be null</t>
   </si>
   <si>
     <t>TC_LEAVE_03</t>
@@ -90,12 +92,18 @@
     <t>Verify Top Navigation Tab Apply is visible</t>
   </si>
   <si>
+    <t>- The Apply tab should be visible</t>
+  </si>
+  <si>
     <t>TC_LEAVE_04</t>
   </si>
   <si>
     <t>Verify Top Navigation Tab My Leave is visible</t>
   </si>
   <si>
+    <t>- The My Leave tab should be visible</t>
+  </si>
+  <si>
     <t>Medium</t>
   </si>
   <si>
@@ -105,30 +113,45 @@
     <t>Verify Top Navigation Tab Entitlements dropdown is visible</t>
   </si>
   <si>
+    <t>- The 'Entitlements' element should be visible</t>
+  </si>
+  <si>
     <t>TC_LEAVE_06</t>
   </si>
   <si>
     <t>Verify Top Navigation Tab Reports dropdown is visible</t>
   </si>
   <si>
+    <t>- The 'Reports' element should be visible</t>
+  </si>
+  <si>
     <t>TC_LEAVE_07</t>
   </si>
   <si>
     <t>Verify Top Navigation Tab Configure dropdown is visible</t>
   </si>
   <si>
+    <t>- The 'Configure' element should be visible</t>
+  </si>
+  <si>
     <t>TC_LEAVE_08</t>
   </si>
   <si>
     <t>Verify Top Navigation Tab Leave List is visible</t>
   </si>
   <si>
+    <t>- The 'Leave List' element should be visible</t>
+  </si>
+  <si>
     <t>TC_LEAVE_09</t>
   </si>
   <si>
     <t>Verify Top Navigation Tab Assign Leave is visible</t>
   </si>
   <si>
+    <t>- The 'Assign Leave' element should be visible</t>
+  </si>
+  <si>
     <t>TC_LEAVE_10</t>
   </si>
   <si>
@@ -138,101 +161,201 @@
     <t>Negative</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Click the Apply tab
+2. Click the Apply button</t>
+  </si>
+  <si>
+    <t>- The 'Leave Type' element should display the text 'Required'</t>
+  </si>
+  <si>
     <t>TC_LEAVE_11</t>
   </si>
   <si>
     <t>Verify From Date input field is visible</t>
   </si>
   <si>
+    <t>- The From Date field should be visible</t>
+  </si>
+  <si>
     <t>TC_LEAVE_12</t>
   </si>
   <si>
     <t>Verify To Date input field is visible</t>
   </si>
   <si>
+    <t>- The To Date field should be visible</t>
+  </si>
+  <si>
     <t>TC_LEAVE_13</t>
   </si>
   <si>
     <t>Verify comments textarea has correct maximum character details</t>
   </si>
   <si>
+    <t>1. Click the Apply tab</t>
+  </si>
+  <si>
+    <t>- The Comments field should be visible</t>
+  </si>
+  <si>
     <t>TC_LEAVE_14</t>
   </si>
   <si>
     <t>Verify calendar icon buttons exist next to date input fields</t>
   </si>
   <si>
+    <t>- The icons.first() should be visible</t>
+  </si>
+  <si>
     <t>TC_LEAVE_15</t>
   </si>
   <si>
     <t>Verify Show with Status multiselect chips exist in My Leave list filters</t>
   </si>
   <si>
+    <t>1. Click the My Leave tab</t>
+  </si>
+  <si>
+    <t>- The status chips should be visible</t>
+  </si>
+  <si>
     <t>TC_LEAVE_16</t>
   </si>
   <si>
     <t>Verify Leave Type dropdown filter is present in My Leave tab</t>
   </si>
   <si>
+    <t>- The 'Leave Type' element should be visible</t>
+  </si>
+  <si>
     <t>TC_LEAVE_17</t>
   </si>
   <si>
     <t>Verify Reset button clears date inputs in My Leave filters</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Click the My Leave tab
+2. Enter '2026-05-01' into the From Date field
+3. Click the 'Reset' element</t>
+  </si>
+  <si>
+    <t>- The val should not equal '2026-05-01'</t>
+  </si>
+  <si>
     <t>TC_LEAVE_18</t>
   </si>
   <si>
     <t>Verify table headers in My Leave results page</t>
   </si>
   <si>
+    <t>- The header row should be visible</t>
+  </si>
+  <si>
     <t>TC_LEAVE_19</t>
   </si>
   <si>
     <t>Verify date validation error message if To Date is before From Date</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Click the Apply tab
+2. Click the From Date field
+3. Press the 'Control+A' key
+4. Press the 'Backspace' key
+5. Enter '2026-10-10' into the From Date field
+6. Press the 'Tab' key
+7. Click the To Date field
+8. Enter '2026-05-10' into the To Date field</t>
+  </si>
+  <si>
+    <t>- The 'To Date' element should display the text 'To date should be after from date'</t>
+  </si>
+  <si>
     <t>TC_LEAVE_20</t>
   </si>
   <si>
     <t>Verify calendar widget opens when From Date input is clicked</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Click the Apply tab
+2. Click the From Date field</t>
+  </si>
+  <si>
+    <t>- The calendar widget should be visible</t>
+  </si>
+  <si>
     <t>TC_LEAVE_21</t>
   </si>
   <si>
     <t>Verify calendar widget opens when To Date input is clicked</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Click the Apply tab
+2. Click the To Date field</t>
+  </si>
+  <si>
     <t>TC_LEAVE_22</t>
   </si>
   <si>
     <t>Verify Leave page header title displays Leave</t>
   </si>
   <si>
+    <t>- The title should contain the text 'Leave'</t>
+  </si>
+  <si>
     <t>TC_LEAVE_23</t>
   </si>
   <si>
     <t>Verify Leave Balance card is shown for specific leave types</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Click the Apply tab
+2. Click the Leave Type dropdown</t>
+  </si>
+  <si>
+    <t>- The balance should be present</t>
+  </si>
+  <si>
     <t>TC_LEAVE_24</t>
   </si>
   <si>
     <t>Verify My Leave list table rows can be scrolled and are visible</t>
   </si>
   <si>
+    <t>- The table should be visible</t>
+  </si>
+  <si>
     <t>TC_LEAVE_25</t>
   </si>
   <si>
     <t>Verify search button on My Leave filters page has correct CSS layout</t>
+  </si>
+  <si>
+    <t>- The submit element should be visible</t>
+  </si>
+  <si>
+    <t>TC_LEAVE_26</t>
+  </si>
+  <si>
+    <t>Verify Leave Type dropdown displays default placeholder text before selection</t>
+  </si>
+  <si>
+    <t>- The text should contain '-- Select --'</t>
+  </si>
+  <si>
+    <t>TC_LEAVE_27</t>
+  </si>
+  <si>
+    <t>Verify Comments textarea accepts multi-line text input</t>
+  </si>
+  <si>
+    <t>- The value should equal 'multiline'</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -252,18 +375,12 @@
     </font>
     <font>
       <b/>
-      <color rgb="FFA51D24"/>
-      <sz val="10"/>
-      <name val="Segoe UI"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF5A6268"/>
+      <color rgb="FF107C41"/>
       <sz val="10"/>
       <name val="Segoe UI"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -277,12 +394,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7DA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2E3E5"/>
+        <fgColor rgb="FFD1E7DD"/>
       </patternFill>
     </fill>
   </fills>
@@ -324,7 +436,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -333,9 +445,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -677,7 +786,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="15" customWidth="1"/>
@@ -783,21 +892,21 @@
         <v>15</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="4" t="s">
-        <v>22</v>
+      <c r="K3" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="4" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>12</v>
@@ -806,33 +915,33 @@
         <v>12</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="K4" s="4" t="s">
-        <v>22</v>
+      <c r="K4" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="5" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>12</v>
@@ -841,33 +950,33 @@
         <v>12</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>22</v>
+        <v>30</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="6" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>12</v>
@@ -876,33 +985,33 @@
         <v>12</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>22</v>
+        <v>30</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="7" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>12</v>
@@ -911,33 +1020,33 @@
         <v>12</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>22</v>
+        <v>30</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="8" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>12</v>
@@ -946,33 +1055,33 @@
         <v>12</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>22</v>
+        <v>30</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="9" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>12</v>
@@ -981,33 +1090,33 @@
         <v>12</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>22</v>
+        <v>30</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="10" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>12</v>
@@ -1016,33 +1125,33 @@
         <v>12</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>22</v>
+        <v>30</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="11" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>12</v>
@@ -1051,33 +1160,33 @@
         <v>12</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>22</v>
+        <v>30</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="12" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
@@ -1086,33 +1195,33 @@
         <v>12</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K12" s="4" t="s">
-        <v>22</v>
+        <v>30</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="13" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>12</v>
@@ -1121,33 +1230,33 @@
         <v>12</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>22</v>
+        <v>30</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="14" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>12</v>
@@ -1156,33 +1265,33 @@
         <v>12</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K14" s="4" t="s">
-        <v>22</v>
+        <v>30</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="15" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>12</v>
@@ -1191,33 +1300,33 @@
         <v>12</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K15" s="4" t="s">
-        <v>22</v>
+        <v>30</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="16" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>12</v>
@@ -1226,33 +1335,33 @@
         <v>12</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K16" s="4" t="s">
-        <v>22</v>
+        <v>30</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="17" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>12</v>
@@ -1261,33 +1370,33 @@
         <v>12</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K17" s="4" t="s">
-        <v>22</v>
+        <v>30</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="18" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>12</v>
@@ -1296,33 +1405,33 @@
         <v>12</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>17</v>
+        <v>74</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K18" s="4" t="s">
-        <v>22</v>
+        <v>30</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="19" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>12</v>
@@ -1331,33 +1440,33 @@
         <v>12</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>17</v>
+        <v>77</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K19" s="4" t="s">
-        <v>22</v>
+        <v>30</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="20" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>12</v>
@@ -1366,33 +1475,33 @@
         <v>12</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>17</v>
+        <v>81</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K20" s="4" t="s">
-        <v>22</v>
+        <v>30</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="21" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>12</v>
@@ -1401,33 +1510,33 @@
         <v>12</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K21" s="4" t="s">
-        <v>22</v>
+        <v>30</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="22" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>12</v>
@@ -1436,33 +1545,33 @@
         <v>12</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>16</v>
+        <v>88</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K22" s="4" t="s">
-        <v>22</v>
+        <v>30</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="23" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>12</v>
@@ -1471,33 +1580,33 @@
         <v>12</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>17</v>
+        <v>91</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K23" s="4" t="s">
-        <v>22</v>
+        <v>30</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="24" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>12</v>
@@ -1506,33 +1615,33 @@
         <v>12</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>17</v>
+        <v>95</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K24" s="4" t="s">
-        <v>22</v>
+        <v>30</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="25" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>67</v>
+        <v>96</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>12</v>
@@ -1541,33 +1650,33 @@
         <v>12</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>17</v>
+        <v>98</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K25" s="4" t="s">
-        <v>22</v>
+        <v>30</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="26" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>12</v>
@@ -1576,28 +1685,98 @@
         <v>12</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>17</v>
+        <v>101</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K26" s="4" t="s">
-        <v>22</v>
+        <v>30</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/Results/TestCases/XLSX/leave_TestCases.xlsx
+++ b/Results/TestCases/XLSX/leave_TestCases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="109">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -71,7 +71,7 @@
     <t>High</t>
   </si>
   <si>
-    <t>PASSED</t>
+    <t>FAILED</t>
   </si>
   <si>
     <t>TC_LEAVE_02</t>
@@ -84,6 +84,9 @@
   </si>
   <si>
     <t>- The leave type should not be null</t>
+  </si>
+  <si>
+    <t>SKIPPED</t>
   </si>
   <si>
     <t>TC_LEAVE_03</t>
@@ -355,7 +358,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -375,12 +378,18 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF107C41"/>
+      <color rgb="FFA51D24"/>
+      <sz val="10"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF5A6268"/>
       <sz val="10"/>
       <name val="Segoe UI"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -394,7 +403,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD1E7DD"/>
+        <fgColor rgb="FFF8D7DA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2E3E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -436,7 +450,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -445,6 +459,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -900,13 +917,13 @@
       <c r="J3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="3" t="s">
-        <v>19</v>
+      <c r="K3" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="4" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>12</v>
@@ -915,13 +932,13 @@
         <v>12</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>15</v>
@@ -930,18 +947,18 @@
         <v>22</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="K4" s="3" t="s">
-        <v>19</v>
+      <c r="K4" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="5" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>12</v>
@@ -950,13 +967,13 @@
         <v>12</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>15</v>
@@ -965,18 +982,18 @@
         <v>22</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="6" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>12</v>
@@ -985,13 +1002,13 @@
         <v>12</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>15</v>
@@ -1000,18 +1017,18 @@
         <v>22</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="7" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>12</v>
@@ -1020,13 +1037,13 @@
         <v>12</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>15</v>
@@ -1035,18 +1052,18 @@
         <v>22</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="8" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>12</v>
@@ -1055,13 +1072,13 @@
         <v>12</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>15</v>
@@ -1070,18 +1087,18 @@
         <v>22</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="9" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>12</v>
@@ -1090,13 +1107,13 @@
         <v>12</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>15</v>
@@ -1105,18 +1122,18 @@
         <v>22</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="10" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>12</v>
@@ -1125,13 +1142,13 @@
         <v>12</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>15</v>
@@ -1140,18 +1157,18 @@
         <v>22</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="11" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>12</v>
@@ -1160,33 +1177,33 @@
         <v>12</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>47</v>
-      </c>
       <c r="G11" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="12" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
@@ -1195,13 +1212,13 @@
         <v>12</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>15</v>
@@ -1210,18 +1227,18 @@
         <v>22</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="13" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>12</v>
@@ -1230,13 +1247,13 @@
         <v>12</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>15</v>
@@ -1245,18 +1262,18 @@
         <v>22</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="14" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>12</v>
@@ -1265,33 +1282,33 @@
         <v>12</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="15" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>12</v>
@@ -1300,13 +1317,13 @@
         <v>12</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>15</v>
@@ -1315,18 +1332,18 @@
         <v>22</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="16" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>12</v>
@@ -1335,33 +1352,33 @@
         <v>12</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="17" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>12</v>
@@ -1370,33 +1387,33 @@
         <v>12</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="18" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>12</v>
@@ -1405,33 +1422,33 @@
         <v>12</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="19" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>12</v>
@@ -1440,33 +1457,33 @@
         <v>12</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="20" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>12</v>
@@ -1475,33 +1492,33 @@
         <v>12</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="21" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>12</v>
@@ -1510,68 +1527,68 @@
         <v>12</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="22" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>85</v>
-      </c>
       <c r="J22" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
+      </c>
+      <c r="K22" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="23" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>12</v>
@@ -1580,13 +1597,13 @@
         <v>12</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>15</v>
@@ -1595,18 +1612,18 @@
         <v>22</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="24" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>12</v>
@@ -1615,33 +1632,33 @@
         <v>12</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="25" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>12</v>
@@ -1650,33 +1667,33 @@
         <v>12</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
+      </c>
+      <c r="K25" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="26" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>12</v>
@@ -1685,33 +1702,33 @@
         <v>12</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
+      </c>
+      <c r="K26" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="27" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>12</v>
@@ -1720,33 +1737,33 @@
         <v>12</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
+      </c>
+      <c r="K27" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="28" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>12</v>
@@ -1755,28 +1772,28 @@
         <v>12</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K28" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
+      </c>
+      <c r="K28" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
